--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ergebnis-ValueSet für die Mikroskopie: mikroskopisch beobachtete Morphologie ohne taxonomische Zuordnung, etwa grampositive Kokken in Haufen oder gramnegative Stäbchen.</t>
+    <t>Ergebnis-ValueSet für die Mikroskopie: die mikroskopisch beobachtete morphologische Gruppe, etwa grampositive Kokken in Haufen oder gramnegative Stäbchen. Eine Speziesidentifizierung gehört nicht hierher, auch wenn sie mikroskopisch gestellt wurde.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,12 +102,42 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>61609004</t>
+  </si>
+  <si>
+    <t>Gram-positive cocci in chains (finding)</t>
+  </si>
+  <si>
+    <t>70003006</t>
+  </si>
+  <si>
+    <t>Gram-positive cocci in clusters (finding)</t>
+  </si>
+  <si>
+    <t>1359949003</t>
+  </si>
+  <si>
+    <t>Gram-positive cocci in pair (finding)</t>
+  </si>
+  <si>
+    <t>734444009</t>
+  </si>
+  <si>
+    <t>Gram-positive cocci in chains, clusters, and pairs (finding)</t>
+  </si>
+  <si>
     <t>723529006</t>
   </si>
   <si>
     <t>Extracellular Gram-negative diplococcus (finding)</t>
   </si>
   <si>
+    <t>734447002</t>
+  </si>
+  <si>
+    <t>Intracellular Gram-negative diplococcus (finding)</t>
+  </si>
+  <si>
     <t>404509004</t>
   </si>
   <si>
@@ -126,28 +156,52 @@
     <t>Small Gram-negative rods (finding)</t>
   </si>
   <si>
-    <t>61609004</t>
-  </si>
-  <si>
-    <t>Gram-positive cocci in chains (finding)</t>
-  </si>
-  <si>
-    <t>70003006</t>
-  </si>
-  <si>
-    <t>Gram-positive cocci in clusters (finding)</t>
-  </si>
-  <si>
-    <t>734444009</t>
-  </si>
-  <si>
-    <t>Gram-positive cocci in chains, clusters, and pairs (finding)</t>
-  </si>
-  <si>
-    <t>734447002</t>
-  </si>
-  <si>
-    <t>Intracellular Gram-negative diplococcus (finding)</t>
+    <t>59206002</t>
+  </si>
+  <si>
+    <t>Gram-positive coccus (organism)</t>
+  </si>
+  <si>
+    <t>18383003</t>
+  </si>
+  <si>
+    <t>Gram-negative coccus (organism)</t>
+  </si>
+  <si>
+    <t>83514008</t>
+  </si>
+  <si>
+    <t>Gram-positive bacillus (organism)</t>
+  </si>
+  <si>
+    <t>87172008</t>
+  </si>
+  <si>
+    <t>Gram-negative bacillus (organism)</t>
+  </si>
+  <si>
+    <t>11471007</t>
+  </si>
+  <si>
+    <t>Gram-positive diplococcus (organism)</t>
+  </si>
+  <si>
+    <t>115199003</t>
+  </si>
+  <si>
+    <t>Subclass Irregular Non-Sporing Gram Positive Rods (organism)</t>
+  </si>
+  <si>
+    <t>116442009</t>
+  </si>
+  <si>
+    <t>Coryneform bacteria (organism)</t>
+  </si>
+  <si>
+    <t>62093005</t>
+  </si>
+  <si>
+    <t>Yeast (organism)</t>
   </si>
   <si>
     <t>404507002</t>
@@ -190,6 +244,24 @@
   </si>
   <si>
     <t>Septate hyphae of kingdom Fungi detected (finding)</t>
+  </si>
+  <si>
+    <t>27863008</t>
+  </si>
+  <si>
+    <t>No organisms seen (finding)</t>
+  </si>
+  <si>
+    <t>721786009</t>
+  </si>
+  <si>
+    <t>No cells seen (finding)</t>
+  </si>
+  <si>
+    <t>250440009</t>
+  </si>
+  <si>
+    <t>Clue cells present (finding)</t>
   </si>
   <si>
     <t/>
@@ -462,7 +534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -602,15 +674,111 @@
         <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -186,12 +186,6 @@
     <t>Gram-positive diplococcus (organism)</t>
   </si>
   <si>
-    <t>115199003</t>
-  </si>
-  <si>
-    <t>Subclass Irregular Non-Sporing Gram Positive Rods (organism)</t>
-  </si>
-  <si>
     <t>116442009</t>
   </si>
   <si>
@@ -202,6 +196,24 @@
   </si>
   <si>
     <t>Yeast (organism)</t>
+  </si>
+  <si>
+    <t>243365003</t>
+  </si>
+  <si>
+    <t>Acid-fast bacillus (organism)</t>
+  </si>
+  <si>
+    <t>243366002</t>
+  </si>
+  <si>
+    <t>Partially acid-fast bacillus (organism)</t>
+  </si>
+  <si>
+    <t>243367006</t>
+  </si>
+  <si>
+    <t>Acid and alcohol-fast bacillus (organism)</t>
   </si>
   <si>
     <t>404507002</t>
@@ -534,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -770,15 +782,31 @@
         <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
+++ b/ValueSet-mii-vs-mikrobio-morphologie-ergebnis-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
